--- a/Base/Backlog_39.xlsx
+++ b/Base/Backlog_39.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franciscoj\Python_Initial\Pyhton_Web\Base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{111AF108-B14E-4550-9925-59233D607553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58E55CD1-0406-4784-8F9C-9CE3A62DC907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="273" xr2:uid="{89A3EF9E-2AF9-420D-85DF-9BB5B68F651F}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="273" xr2:uid="{89A3EF9E-2AF9-420D-85DF-9BB5B68F651F}"/>
   </bookViews>
   <sheets>
     <sheet name="ITI" sheetId="2" r:id="rId1"/>
     <sheet name="SPN" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ITI!$A$1:$K$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ITI!$A$1:$K$42</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">SPN!$A$1:$J$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="35">
   <si>
     <t>Backlog</t>
   </si>
@@ -143,6 +143,9 @@
   </si>
   <si>
     <t>Higor Jesus</t>
+  </si>
+  <si>
+    <t>Resolvido</t>
   </si>
 </sst>
 </file>
@@ -256,32 +259,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -295,11 +274,33 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -619,25 +620,25 @@
   <dimension ref="A1:K50"/>
   <sheetFormatPr defaultColWidth="9.5703125" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.42578125" style="19" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.28515625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.85546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.5703125" style="1"/>
+    <col min="1" max="1" width="10.85546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.5703125" style="14" customWidth="1"/>
+    <col min="3" max="3" width="13" style="13" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.85546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.140625" style="16" customWidth="1"/>
+    <col min="10" max="10" width="16.140625" style="16" customWidth="1"/>
+    <col min="11" max="11" width="18.5703125" style="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.5703125" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C1" s="6" t="s">
@@ -672,28 +673,28 @@
       <c r="A2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="10" t="s">
         <v>25</v>
       </c>
       <c r="C2" s="9">
         <v>2025</v>
       </c>
-      <c r="D2" s="11">
-        <v>39</v>
-      </c>
-      <c r="E2" s="12">
-        <v>45929</v>
-      </c>
-      <c r="F2" s="10">
+      <c r="D2" s="1">
+        <v>39</v>
+      </c>
+      <c r="E2" s="2">
+        <v>45929</v>
+      </c>
+      <c r="F2" s="11">
         <v>45933</v>
       </c>
       <c r="G2" s="9">
         <v>2873</v>
       </c>
-      <c r="H2" s="13">
-        <v>45901</v>
-      </c>
-      <c r="I2" s="12">
+      <c r="H2" s="3">
+        <v>45901</v>
+      </c>
+      <c r="I2" s="2">
         <v>45929</v>
       </c>
       <c r="J2" s="9" t="s">
@@ -707,28 +708,28 @@
       <c r="A3" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="10" t="s">
         <v>25</v>
       </c>
       <c r="C3" s="9">
         <v>2025</v>
       </c>
-      <c r="D3" s="11">
-        <v>39</v>
-      </c>
-      <c r="E3" s="12">
-        <v>45929</v>
-      </c>
-      <c r="F3" s="10">
+      <c r="D3" s="1">
+        <v>39</v>
+      </c>
+      <c r="E3" s="2">
+        <v>45929</v>
+      </c>
+      <c r="F3" s="11">
         <v>45933</v>
       </c>
       <c r="G3" s="9">
         <v>2847</v>
       </c>
-      <c r="H3" s="13">
-        <v>45901</v>
-      </c>
-      <c r="I3" s="12">
+      <c r="H3" s="3">
+        <v>45901</v>
+      </c>
+      <c r="I3" s="2">
         <v>45929</v>
       </c>
       <c r="J3" s="9" t="s">
@@ -742,28 +743,28 @@
       <c r="A4" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="10" t="s">
         <v>25</v>
       </c>
       <c r="C4" s="9">
         <v>2025</v>
       </c>
-      <c r="D4" s="11">
-        <v>39</v>
-      </c>
-      <c r="E4" s="12">
-        <v>45929</v>
-      </c>
-      <c r="F4" s="10">
+      <c r="D4" s="1">
+        <v>39</v>
+      </c>
+      <c r="E4" s="2">
+        <v>45929</v>
+      </c>
+      <c r="F4" s="11">
         <v>45933</v>
       </c>
       <c r="G4" s="9">
         <v>2366</v>
       </c>
-      <c r="H4" s="13">
-        <v>45901</v>
-      </c>
-      <c r="I4" s="12">
+      <c r="H4" s="3">
+        <v>45901</v>
+      </c>
+      <c r="I4" s="2">
         <v>45929</v>
       </c>
       <c r="J4" s="9" t="s">
@@ -777,28 +778,28 @@
       <c r="A5" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="10" t="s">
         <v>25</v>
       </c>
       <c r="C5" s="9">
         <v>2025</v>
       </c>
-      <c r="D5" s="11">
-        <v>39</v>
-      </c>
-      <c r="E5" s="12">
-        <v>45929</v>
-      </c>
-      <c r="F5" s="10">
+      <c r="D5" s="1">
+        <v>39</v>
+      </c>
+      <c r="E5" s="2">
+        <v>45929</v>
+      </c>
+      <c r="F5" s="11">
         <v>45933</v>
       </c>
       <c r="G5" s="9">
         <v>2237</v>
       </c>
-      <c r="H5" s="13">
-        <v>45901</v>
-      </c>
-      <c r="I5" s="12">
+      <c r="H5" s="3">
+        <v>45901</v>
+      </c>
+      <c r="I5" s="2">
         <v>45929</v>
       </c>
       <c r="J5" s="9" t="s">
@@ -812,28 +813,28 @@
       <c r="A6" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="10" t="s">
         <v>25</v>
       </c>
       <c r="C6" s="9">
         <v>2025</v>
       </c>
-      <c r="D6" s="11">
-        <v>39</v>
-      </c>
-      <c r="E6" s="12">
-        <v>45929</v>
-      </c>
-      <c r="F6" s="10">
+      <c r="D6" s="1">
+        <v>39</v>
+      </c>
+      <c r="E6" s="2">
+        <v>45929</v>
+      </c>
+      <c r="F6" s="11">
         <v>45933</v>
       </c>
       <c r="G6" s="9">
         <v>2179</v>
       </c>
-      <c r="H6" s="13">
-        <v>45901</v>
-      </c>
-      <c r="I6" s="12">
+      <c r="H6" s="3">
+        <v>45901</v>
+      </c>
+      <c r="I6" s="2">
         <v>45929</v>
       </c>
       <c r="J6" s="9" t="s">
@@ -847,28 +848,28 @@
       <c r="A7" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="10" t="s">
         <v>25</v>
       </c>
       <c r="C7" s="9">
         <v>2025</v>
       </c>
-      <c r="D7" s="11">
-        <v>39</v>
-      </c>
-      <c r="E7" s="12">
-        <v>45929</v>
-      </c>
-      <c r="F7" s="10">
+      <c r="D7" s="1">
+        <v>39</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45929</v>
+      </c>
+      <c r="F7" s="11">
         <v>45933</v>
       </c>
       <c r="G7" s="9">
         <v>2174</v>
       </c>
-      <c r="H7" s="13">
-        <v>45901</v>
-      </c>
-      <c r="I7" s="12">
+      <c r="H7" s="3">
+        <v>45901</v>
+      </c>
+      <c r="I7" s="2">
         <v>45929</v>
       </c>
       <c r="J7" s="9" t="s">
@@ -882,28 +883,28 @@
       <c r="A8" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="10" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="9">
         <v>2025</v>
       </c>
-      <c r="D8" s="11">
-        <v>39</v>
-      </c>
-      <c r="E8" s="12">
-        <v>45929</v>
-      </c>
-      <c r="F8" s="10">
+      <c r="D8" s="1">
+        <v>39</v>
+      </c>
+      <c r="E8" s="2">
+        <v>45929</v>
+      </c>
+      <c r="F8" s="11">
         <v>45933</v>
       </c>
       <c r="G8" s="9">
         <v>2006</v>
       </c>
-      <c r="H8" s="13">
-        <v>45901</v>
-      </c>
-      <c r="I8" s="12">
+      <c r="H8" s="3">
+        <v>45901</v>
+      </c>
+      <c r="I8" s="2">
         <v>45929</v>
       </c>
       <c r="J8" s="9" t="s">
@@ -917,28 +918,28 @@
       <c r="A9" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="10" t="s">
         <v>25</v>
       </c>
       <c r="C9" s="9">
         <v>2025</v>
       </c>
-      <c r="D9" s="11">
-        <v>39</v>
-      </c>
-      <c r="E9" s="12">
-        <v>45929</v>
-      </c>
-      <c r="F9" s="10">
+      <c r="D9" s="1">
+        <v>39</v>
+      </c>
+      <c r="E9" s="2">
+        <v>45929</v>
+      </c>
+      <c r="F9" s="11">
         <v>45933</v>
       </c>
       <c r="G9" s="9">
         <v>1835</v>
       </c>
-      <c r="H9" s="13">
-        <v>45901</v>
-      </c>
-      <c r="I9" s="12">
+      <c r="H9" s="3">
+        <v>45901</v>
+      </c>
+      <c r="I9" s="2">
         <v>45929</v>
       </c>
       <c r="J9" s="9" t="s">
@@ -952,28 +953,28 @@
       <c r="A10" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="10" t="s">
         <v>25</v>
       </c>
       <c r="C10" s="9">
         <v>2025</v>
       </c>
-      <c r="D10" s="11">
-        <v>39</v>
-      </c>
-      <c r="E10" s="12">
-        <v>45929</v>
-      </c>
-      <c r="F10" s="10">
+      <c r="D10" s="1">
+        <v>39</v>
+      </c>
+      <c r="E10" s="2">
+        <v>45929</v>
+      </c>
+      <c r="F10" s="11">
         <v>45933</v>
       </c>
       <c r="G10" s="9">
         <v>1748</v>
       </c>
-      <c r="H10" s="13">
-        <v>45901</v>
-      </c>
-      <c r="I10" s="12">
+      <c r="H10" s="3">
+        <v>45901</v>
+      </c>
+      <c r="I10" s="2">
         <v>45929</v>
       </c>
       <c r="J10" s="9" t="s">
@@ -987,28 +988,28 @@
       <c r="A11" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="10" t="s">
         <v>25</v>
       </c>
       <c r="C11" s="9">
         <v>2025</v>
       </c>
-      <c r="D11" s="11">
-        <v>39</v>
-      </c>
-      <c r="E11" s="12">
-        <v>45929</v>
-      </c>
-      <c r="F11" s="10">
+      <c r="D11" s="1">
+        <v>39</v>
+      </c>
+      <c r="E11" s="2">
+        <v>45929</v>
+      </c>
+      <c r="F11" s="11">
         <v>45933</v>
       </c>
       <c r="G11" s="9">
         <v>238</v>
       </c>
-      <c r="H11" s="13">
-        <v>45901</v>
-      </c>
-      <c r="I11" s="12">
+      <c r="H11" s="3">
+        <v>45901</v>
+      </c>
+      <c r="I11" s="2">
         <v>45929</v>
       </c>
       <c r="J11" s="9" t="s">
@@ -1022,28 +1023,28 @@
       <c r="A12" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="10" t="s">
         <v>20</v>
       </c>
       <c r="C12" s="9">
         <v>2025</v>
       </c>
-      <c r="D12" s="11">
-        <v>39</v>
-      </c>
-      <c r="E12" s="12">
-        <v>45929</v>
-      </c>
-      <c r="F12" s="10">
+      <c r="D12" s="1">
+        <v>39</v>
+      </c>
+      <c r="E12" s="2">
+        <v>45929</v>
+      </c>
+      <c r="F12" s="11">
         <v>45933</v>
       </c>
       <c r="G12" s="9">
         <v>1102</v>
       </c>
-      <c r="H12" s="13">
-        <v>45901</v>
-      </c>
-      <c r="I12" s="12">
+      <c r="H12" s="3">
+        <v>45901</v>
+      </c>
+      <c r="I12" s="2">
         <v>45929</v>
       </c>
       <c r="J12" s="9" t="s">
@@ -1057,32 +1058,32 @@
       <c r="A13" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="10" t="s">
         <v>26</v>
       </c>
       <c r="C13" s="9">
         <v>2025</v>
       </c>
-      <c r="D13" s="11">
-        <v>39</v>
-      </c>
-      <c r="E13" s="12">
-        <v>45929</v>
-      </c>
-      <c r="F13" s="10">
+      <c r="D13" s="1">
+        <v>39</v>
+      </c>
+      <c r="E13" s="2">
+        <v>45929</v>
+      </c>
+      <c r="F13" s="11">
         <v>45933</v>
       </c>
       <c r="G13" s="9">
         <v>2810</v>
       </c>
-      <c r="H13" s="13">
-        <v>45901</v>
-      </c>
-      <c r="I13" s="12">
+      <c r="H13" s="3">
+        <v>45901</v>
+      </c>
+      <c r="I13" s="2">
         <v>45929</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="K13" s="9" t="s">
         <v>11</v>
@@ -1092,32 +1093,32 @@
       <c r="A14" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C14" s="9">
         <v>2025</v>
       </c>
-      <c r="D14" s="11">
-        <v>39</v>
-      </c>
-      <c r="E14" s="12">
-        <v>45929</v>
-      </c>
-      <c r="F14" s="10">
+      <c r="D14" s="1">
+        <v>39</v>
+      </c>
+      <c r="E14" s="2">
+        <v>45929</v>
+      </c>
+      <c r="F14" s="11">
         <v>45933</v>
       </c>
       <c r="G14" s="9">
         <v>2490</v>
       </c>
-      <c r="H14" s="13">
-        <v>45901</v>
-      </c>
-      <c r="I14" s="12">
+      <c r="H14" s="3">
+        <v>45901</v>
+      </c>
+      <c r="I14" s="2">
         <v>45929</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="K14" s="9" t="s">
         <v>11</v>
@@ -1127,32 +1128,32 @@
       <c r="A15" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="B15" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C15" s="9">
         <v>2025</v>
       </c>
-      <c r="D15" s="11">
-        <v>39</v>
-      </c>
-      <c r="E15" s="12">
-        <v>45929</v>
-      </c>
-      <c r="F15" s="10">
+      <c r="D15" s="1">
+        <v>39</v>
+      </c>
+      <c r="E15" s="2">
+        <v>45929</v>
+      </c>
+      <c r="F15" s="11">
         <v>45933</v>
       </c>
       <c r="G15" s="9">
         <v>2279</v>
       </c>
-      <c r="H15" s="13">
-        <v>45901</v>
-      </c>
-      <c r="I15" s="12">
+      <c r="H15" s="3">
+        <v>45901</v>
+      </c>
+      <c r="I15" s="2">
         <v>45929</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="K15" s="9" t="s">
         <v>11</v>
@@ -1162,32 +1163,32 @@
       <c r="A16" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C16" s="9">
         <v>2025</v>
       </c>
-      <c r="D16" s="11">
-        <v>39</v>
-      </c>
-      <c r="E16" s="12">
-        <v>45929</v>
-      </c>
-      <c r="F16" s="10">
+      <c r="D16" s="1">
+        <v>39</v>
+      </c>
+      <c r="E16" s="2">
+        <v>45929</v>
+      </c>
+      <c r="F16" s="11">
         <v>45933</v>
       </c>
       <c r="G16" s="9">
         <v>1743</v>
       </c>
-      <c r="H16" s="13">
-        <v>45901</v>
-      </c>
-      <c r="I16" s="12">
+      <c r="H16" s="3">
+        <v>45901</v>
+      </c>
+      <c r="I16" s="2">
         <v>45929</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="K16" s="9" t="s">
         <v>11</v>
@@ -1197,28 +1198,28 @@
       <c r="A17" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="10" t="s">
         <v>21</v>
       </c>
       <c r="C17" s="9">
         <v>2025</v>
       </c>
-      <c r="D17" s="11">
-        <v>39</v>
-      </c>
-      <c r="E17" s="12">
-        <v>45929</v>
-      </c>
-      <c r="F17" s="10">
+      <c r="D17" s="1">
+        <v>39</v>
+      </c>
+      <c r="E17" s="2">
+        <v>45929</v>
+      </c>
+      <c r="F17" s="11">
         <v>45933</v>
       </c>
       <c r="G17" s="9">
         <v>2825</v>
       </c>
-      <c r="H17" s="13">
-        <v>45901</v>
-      </c>
-      <c r="I17" s="12">
+      <c r="H17" s="3">
+        <v>45901</v>
+      </c>
+      <c r="I17" s="2">
         <v>45929</v>
       </c>
       <c r="J17" s="9" t="s">
@@ -1232,28 +1233,28 @@
       <c r="A18" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="B18" s="10" t="s">
         <v>21</v>
       </c>
       <c r="C18" s="9">
         <v>2025</v>
       </c>
-      <c r="D18" s="11">
-        <v>39</v>
-      </c>
-      <c r="E18" s="12">
-        <v>45929</v>
-      </c>
-      <c r="F18" s="10">
+      <c r="D18" s="1">
+        <v>39</v>
+      </c>
+      <c r="E18" s="2">
+        <v>45929</v>
+      </c>
+      <c r="F18" s="11">
         <v>45933</v>
       </c>
       <c r="G18" s="9">
         <v>1159</v>
       </c>
-      <c r="H18" s="13">
-        <v>45901</v>
-      </c>
-      <c r="I18" s="12">
+      <c r="H18" s="3">
+        <v>45901</v>
+      </c>
+      <c r="I18" s="2">
         <v>45929</v>
       </c>
       <c r="J18" s="9" t="s">
@@ -1267,32 +1268,32 @@
       <c r="A19" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="10" t="s">
         <v>22</v>
       </c>
       <c r="C19" s="9">
         <v>2025</v>
       </c>
-      <c r="D19" s="11">
-        <v>39</v>
-      </c>
-      <c r="E19" s="12">
-        <v>45929</v>
-      </c>
-      <c r="F19" s="10">
+      <c r="D19" s="1">
+        <v>39</v>
+      </c>
+      <c r="E19" s="2">
+        <v>45929</v>
+      </c>
+      <c r="F19" s="11">
         <v>45933</v>
       </c>
       <c r="G19" s="9">
         <v>2095</v>
       </c>
-      <c r="H19" s="13">
-        <v>45901</v>
-      </c>
-      <c r="I19" s="12">
+      <c r="H19" s="3">
+        <v>45901</v>
+      </c>
+      <c r="I19" s="2">
         <v>45929</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="K19" s="9" t="s">
         <v>11</v>
@@ -1302,32 +1303,32 @@
       <c r="A20" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="B20" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C20" s="9">
         <v>2025</v>
       </c>
-      <c r="D20" s="11">
-        <v>39</v>
-      </c>
-      <c r="E20" s="12">
-        <v>45929</v>
-      </c>
-      <c r="F20" s="10">
+      <c r="D20" s="1">
+        <v>39</v>
+      </c>
+      <c r="E20" s="2">
+        <v>45929</v>
+      </c>
+      <c r="F20" s="11">
         <v>45933</v>
       </c>
       <c r="G20" s="9">
         <v>2848</v>
       </c>
-      <c r="H20" s="13">
-        <v>45901</v>
-      </c>
-      <c r="I20" s="12">
+      <c r="H20" s="3">
+        <v>45901</v>
+      </c>
+      <c r="I20" s="2">
         <v>45929</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="K20" s="9" t="s">
         <v>11</v>
@@ -1337,28 +1338,28 @@
       <c r="A21" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B21" s="17" t="s">
+      <c r="B21" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C21" s="9">
         <v>2025</v>
       </c>
-      <c r="D21" s="11">
-        <v>39</v>
-      </c>
-      <c r="E21" s="12">
-        <v>45929</v>
-      </c>
-      <c r="F21" s="10">
+      <c r="D21" s="1">
+        <v>39</v>
+      </c>
+      <c r="E21" s="2">
+        <v>45929</v>
+      </c>
+      <c r="F21" s="11">
         <v>45933</v>
       </c>
       <c r="G21" s="9">
         <v>2814</v>
       </c>
-      <c r="H21" s="13">
-        <v>45901</v>
-      </c>
-      <c r="I21" s="12">
+      <c r="H21" s="3">
+        <v>45901</v>
+      </c>
+      <c r="I21" s="2">
         <v>45929</v>
       </c>
       <c r="J21" s="9" t="s">
@@ -1372,28 +1373,28 @@
       <c r="A22" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B22" s="17" t="s">
+      <c r="B22" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C22" s="9">
         <v>2025</v>
       </c>
-      <c r="D22" s="11">
-        <v>39</v>
-      </c>
-      <c r="E22" s="12">
-        <v>45929</v>
-      </c>
-      <c r="F22" s="10">
+      <c r="D22" s="1">
+        <v>39</v>
+      </c>
+      <c r="E22" s="2">
+        <v>45929</v>
+      </c>
+      <c r="F22" s="11">
         <v>45933</v>
       </c>
       <c r="G22" s="9">
         <v>2458</v>
       </c>
-      <c r="H22" s="13">
-        <v>45901</v>
-      </c>
-      <c r="I22" s="12">
+      <c r="H22" s="3">
+        <v>45901</v>
+      </c>
+      <c r="I22" s="2">
         <v>45929</v>
       </c>
       <c r="J22" s="9" t="s">
@@ -1407,32 +1408,32 @@
       <c r="A23" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C23" s="9">
         <v>2025</v>
       </c>
-      <c r="D23" s="11">
-        <v>39</v>
-      </c>
-      <c r="E23" s="12">
-        <v>45929</v>
-      </c>
-      <c r="F23" s="10">
+      <c r="D23" s="1">
+        <v>39</v>
+      </c>
+      <c r="E23" s="2">
+        <v>45929</v>
+      </c>
+      <c r="F23" s="11">
         <v>45933</v>
       </c>
       <c r="G23" s="9">
         <v>2231</v>
       </c>
-      <c r="H23" s="13">
-        <v>45901</v>
-      </c>
-      <c r="I23" s="12">
+      <c r="H23" s="3">
+        <v>45901</v>
+      </c>
+      <c r="I23" s="2">
         <v>45929</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="K23" s="9" t="s">
         <v>11</v>
@@ -1442,28 +1443,28 @@
       <c r="A24" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B24" s="17" t="s">
+      <c r="B24" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C24" s="9">
         <v>2025</v>
       </c>
-      <c r="D24" s="11">
-        <v>39</v>
-      </c>
-      <c r="E24" s="12">
-        <v>45929</v>
-      </c>
-      <c r="F24" s="10">
+      <c r="D24" s="1">
+        <v>39</v>
+      </c>
+      <c r="E24" s="2">
+        <v>45929</v>
+      </c>
+      <c r="F24" s="11">
         <v>45933</v>
       </c>
       <c r="G24" s="9">
         <v>1010</v>
       </c>
-      <c r="H24" s="13">
-        <v>45901</v>
-      </c>
-      <c r="I24" s="12">
+      <c r="H24" s="3">
+        <v>45901</v>
+      </c>
+      <c r="I24" s="2">
         <v>45929</v>
       </c>
       <c r="J24" s="9" t="s">
@@ -1477,32 +1478,32 @@
       <c r="A25" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B25" s="17" t="s">
+      <c r="B25" s="10" t="s">
         <v>27</v>
       </c>
       <c r="C25" s="9">
         <v>2025</v>
       </c>
-      <c r="D25" s="11">
-        <v>39</v>
-      </c>
-      <c r="E25" s="12">
-        <v>45929</v>
-      </c>
-      <c r="F25" s="10">
+      <c r="D25" s="1">
+        <v>39</v>
+      </c>
+      <c r="E25" s="2">
+        <v>45929</v>
+      </c>
+      <c r="F25" s="11">
         <v>45933</v>
       </c>
       <c r="G25" s="9">
         <v>344693</v>
       </c>
-      <c r="H25" s="13">
+      <c r="H25" s="3">
         <v>45870</v>
       </c>
-      <c r="I25" s="12">
+      <c r="I25" s="2">
         <v>45929</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="K25" s="9" t="s">
         <v>11</v>
@@ -1512,32 +1513,32 @@
       <c r="A26" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B26" s="17" t="s">
+      <c r="B26" s="10" t="s">
         <v>29</v>
       </c>
       <c r="C26" s="9">
         <v>2025</v>
       </c>
-      <c r="D26" s="11">
-        <v>39</v>
-      </c>
-      <c r="E26" s="12">
-        <v>45929</v>
-      </c>
-      <c r="F26" s="10">
+      <c r="D26" s="1">
+        <v>39</v>
+      </c>
+      <c r="E26" s="2">
+        <v>45929</v>
+      </c>
+      <c r="F26" s="11">
         <v>45933</v>
       </c>
       <c r="G26" s="9">
         <v>2725</v>
       </c>
-      <c r="H26" s="13">
-        <v>45901</v>
-      </c>
-      <c r="I26" s="12">
+      <c r="H26" s="3">
+        <v>45901</v>
+      </c>
+      <c r="I26" s="2">
         <v>45929</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="K26" s="9" t="s">
         <v>11</v>
@@ -1547,28 +1548,28 @@
       <c r="A27" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B27" s="17" t="s">
+      <c r="B27" s="10" t="s">
         <v>29</v>
       </c>
       <c r="C27" s="9">
         <v>2025</v>
       </c>
-      <c r="D27" s="11">
-        <v>39</v>
-      </c>
-      <c r="E27" s="12">
-        <v>45929</v>
-      </c>
-      <c r="F27" s="10">
+      <c r="D27" s="1">
+        <v>39</v>
+      </c>
+      <c r="E27" s="2">
+        <v>45929</v>
+      </c>
+      <c r="F27" s="11">
         <v>45933</v>
       </c>
       <c r="G27" s="9">
         <v>344437</v>
       </c>
-      <c r="H27" s="13">
+      <c r="H27" s="3">
         <v>45870</v>
       </c>
-      <c r="I27" s="12">
+      <c r="I27" s="2">
         <v>45929</v>
       </c>
       <c r="J27" s="9" t="s">
@@ -1582,28 +1583,28 @@
       <c r="A28" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B28" s="18" t="s">
+      <c r="B28" s="10" t="s">
         <v>30</v>
       </c>
       <c r="C28" s="9">
         <v>2025</v>
       </c>
-      <c r="D28" s="11">
-        <v>39</v>
-      </c>
-      <c r="E28" s="12">
-        <v>45929</v>
-      </c>
-      <c r="F28" s="10">
+      <c r="D28" s="1">
+        <v>39</v>
+      </c>
+      <c r="E28" s="2">
+        <v>45929</v>
+      </c>
+      <c r="F28" s="11">
         <v>45933</v>
       </c>
       <c r="G28" s="9">
         <v>1045</v>
       </c>
-      <c r="H28" s="13">
-        <v>45901</v>
-      </c>
-      <c r="I28" s="12">
+      <c r="H28" s="3">
+        <v>45901</v>
+      </c>
+      <c r="I28" s="2">
         <v>45929</v>
       </c>
       <c r="J28" s="9" t="s">
@@ -1617,28 +1618,28 @@
       <c r="A29" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B29" s="18" t="s">
+      <c r="B29" s="10" t="s">
         <v>31</v>
       </c>
       <c r="C29" s="9">
         <v>2025</v>
       </c>
-      <c r="D29" s="11">
-        <v>39</v>
-      </c>
-      <c r="E29" s="12">
-        <v>45929</v>
-      </c>
-      <c r="F29" s="10">
+      <c r="D29" s="1">
+        <v>39</v>
+      </c>
+      <c r="E29" s="2">
+        <v>45929</v>
+      </c>
+      <c r="F29" s="11">
         <v>45933</v>
       </c>
       <c r="G29" s="9">
         <v>2566</v>
       </c>
-      <c r="H29" s="13">
-        <v>45901</v>
-      </c>
-      <c r="I29" s="12">
+      <c r="H29" s="3">
+        <v>45901</v>
+      </c>
+      <c r="I29" s="2">
         <v>45929</v>
       </c>
       <c r="J29" s="9" t="s">
@@ -1652,28 +1653,28 @@
       <c r="A30" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B30" s="18" t="s">
+      <c r="B30" s="10" t="s">
         <v>31</v>
       </c>
       <c r="C30" s="9">
         <v>2025</v>
       </c>
-      <c r="D30" s="11">
-        <v>39</v>
-      </c>
-      <c r="E30" s="12">
-        <v>45929</v>
-      </c>
-      <c r="F30" s="10">
+      <c r="D30" s="1">
+        <v>39</v>
+      </c>
+      <c r="E30" s="2">
+        <v>45929</v>
+      </c>
+      <c r="F30" s="11">
         <v>45933</v>
       </c>
       <c r="G30" s="9">
         <v>2048</v>
       </c>
-      <c r="H30" s="13">
-        <v>45901</v>
-      </c>
-      <c r="I30" s="12">
+      <c r="H30" s="3">
+        <v>45901</v>
+      </c>
+      <c r="I30" s="2">
         <v>45929</v>
       </c>
       <c r="J30" s="9" t="s">
@@ -1687,32 +1688,32 @@
       <c r="A31" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B31" s="18" t="s">
+      <c r="B31" s="10" t="s">
         <v>31</v>
       </c>
       <c r="C31" s="9">
         <v>2025</v>
       </c>
-      <c r="D31" s="11">
-        <v>39</v>
-      </c>
-      <c r="E31" s="12">
-        <v>45929</v>
-      </c>
-      <c r="F31" s="10">
+      <c r="D31" s="1">
+        <v>39</v>
+      </c>
+      <c r="E31" s="2">
+        <v>45929</v>
+      </c>
+      <c r="F31" s="11">
         <v>45933</v>
       </c>
       <c r="G31" s="9">
         <v>1720</v>
       </c>
-      <c r="H31" s="13">
-        <v>45901</v>
-      </c>
-      <c r="I31" s="12">
+      <c r="H31" s="3">
+        <v>45901</v>
+      </c>
+      <c r="I31" s="2">
         <v>45929</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="K31" s="9" t="s">
         <v>11</v>
@@ -1722,28 +1723,28 @@
       <c r="A32" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B32" s="17" t="s">
+      <c r="B32" s="10" t="s">
         <v>23</v>
       </c>
       <c r="C32" s="9">
         <v>2025</v>
       </c>
-      <c r="D32" s="11">
-        <v>39</v>
-      </c>
-      <c r="E32" s="12">
-        <v>45929</v>
-      </c>
-      <c r="F32" s="10">
+      <c r="D32" s="1">
+        <v>39</v>
+      </c>
+      <c r="E32" s="2">
+        <v>45929</v>
+      </c>
+      <c r="F32" s="11">
         <v>45933</v>
       </c>
       <c r="G32" s="9">
         <v>2440</v>
       </c>
-      <c r="H32" s="13">
-        <v>45901</v>
-      </c>
-      <c r="I32" s="12">
+      <c r="H32" s="3">
+        <v>45901</v>
+      </c>
+      <c r="I32" s="2">
         <v>45929</v>
       </c>
       <c r="J32" s="9" t="s">
@@ -1757,32 +1758,32 @@
       <c r="A33" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B33" s="17" t="s">
+      <c r="B33" s="10" t="s">
         <v>24</v>
       </c>
       <c r="C33" s="9">
         <v>2025</v>
       </c>
-      <c r="D33" s="11">
-        <v>39</v>
-      </c>
-      <c r="E33" s="12">
-        <v>45929</v>
-      </c>
-      <c r="F33" s="10">
+      <c r="D33" s="1">
+        <v>39</v>
+      </c>
+      <c r="E33" s="2">
+        <v>45929</v>
+      </c>
+      <c r="F33" s="11">
         <v>45933</v>
       </c>
       <c r="G33" s="9">
         <v>2639</v>
       </c>
-      <c r="H33" s="13">
-        <v>45901</v>
-      </c>
-      <c r="I33" s="12">
+      <c r="H33" s="3">
+        <v>45901</v>
+      </c>
+      <c r="I33" s="2">
         <v>45929</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="K33" s="9" t="s">
         <v>11</v>
@@ -1792,28 +1793,28 @@
       <c r="A34" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B34" s="18" t="s">
+      <c r="B34" s="10" t="s">
         <v>32</v>
       </c>
       <c r="C34" s="9">
         <v>2025</v>
       </c>
-      <c r="D34" s="11">
-        <v>39</v>
-      </c>
-      <c r="E34" s="12">
-        <v>45929</v>
-      </c>
-      <c r="F34" s="10">
+      <c r="D34" s="1">
+        <v>39</v>
+      </c>
+      <c r="E34" s="2">
+        <v>45929</v>
+      </c>
+      <c r="F34" s="11">
         <v>45933</v>
       </c>
       <c r="G34" s="9">
         <v>2932</v>
       </c>
-      <c r="H34" s="13">
-        <v>45901</v>
-      </c>
-      <c r="I34" s="12">
+      <c r="H34" s="3">
+        <v>45901</v>
+      </c>
+      <c r="I34" s="2">
         <v>45929</v>
       </c>
       <c r="J34" s="9" t="s">
@@ -1827,28 +1828,28 @@
       <c r="A35" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B35" s="18" t="s">
+      <c r="B35" s="10" t="s">
         <v>32</v>
       </c>
       <c r="C35" s="9">
         <v>2025</v>
       </c>
-      <c r="D35" s="11">
-        <v>39</v>
-      </c>
-      <c r="E35" s="12">
-        <v>45929</v>
-      </c>
-      <c r="F35" s="10">
+      <c r="D35" s="1">
+        <v>39</v>
+      </c>
+      <c r="E35" s="2">
+        <v>45929</v>
+      </c>
+      <c r="F35" s="11">
         <v>45933</v>
       </c>
       <c r="G35" s="9">
         <v>2549</v>
       </c>
-      <c r="H35" s="13">
-        <v>45901</v>
-      </c>
-      <c r="I35" s="12">
+      <c r="H35" s="3">
+        <v>45901</v>
+      </c>
+      <c r="I35" s="2">
         <v>45929</v>
       </c>
       <c r="J35" s="9" t="s">
@@ -1862,28 +1863,28 @@
       <c r="A36" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B36" s="18" t="s">
+      <c r="B36" s="10" t="s">
         <v>32</v>
       </c>
       <c r="C36" s="9">
         <v>2025</v>
       </c>
-      <c r="D36" s="11">
-        <v>39</v>
-      </c>
-      <c r="E36" s="12">
-        <v>45929</v>
-      </c>
-      <c r="F36" s="10">
+      <c r="D36" s="1">
+        <v>39</v>
+      </c>
+      <c r="E36" s="2">
+        <v>45929</v>
+      </c>
+      <c r="F36" s="11">
         <v>45933</v>
       </c>
       <c r="G36" s="9">
         <v>2522</v>
       </c>
-      <c r="H36" s="13">
-        <v>45901</v>
-      </c>
-      <c r="I36" s="12">
+      <c r="H36" s="3">
+        <v>45901</v>
+      </c>
+      <c r="I36" s="2">
         <v>45929</v>
       </c>
       <c r="J36" s="9" t="s">
@@ -1897,28 +1898,28 @@
       <c r="A37" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B37" s="18" t="s">
+      <c r="B37" s="10" t="s">
         <v>32</v>
       </c>
       <c r="C37" s="9">
         <v>2025</v>
       </c>
-      <c r="D37" s="11">
-        <v>39</v>
-      </c>
-      <c r="E37" s="12">
-        <v>45929</v>
-      </c>
-      <c r="F37" s="10">
+      <c r="D37" s="1">
+        <v>39</v>
+      </c>
+      <c r="E37" s="2">
+        <v>45929</v>
+      </c>
+      <c r="F37" s="11">
         <v>45933</v>
       </c>
       <c r="G37" s="9">
         <v>2128</v>
       </c>
-      <c r="H37" s="13">
-        <v>45901</v>
-      </c>
-      <c r="I37" s="12">
+      <c r="H37" s="3">
+        <v>45901</v>
+      </c>
+      <c r="I37" s="2">
         <v>45929</v>
       </c>
       <c r="J37" s="9" t="s">
@@ -1932,28 +1933,28 @@
       <c r="A38" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B38" s="18" t="s">
+      <c r="B38" s="10" t="s">
         <v>32</v>
       </c>
       <c r="C38" s="9">
         <v>2025</v>
       </c>
-      <c r="D38" s="11">
-        <v>39</v>
-      </c>
-      <c r="E38" s="12">
-        <v>45929</v>
-      </c>
-      <c r="F38" s="10">
+      <c r="D38" s="1">
+        <v>39</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45929</v>
+      </c>
+      <c r="F38" s="11">
         <v>45933</v>
       </c>
       <c r="G38" s="9">
         <v>2015</v>
       </c>
-      <c r="H38" s="13">
-        <v>45901</v>
-      </c>
-      <c r="I38" s="12">
+      <c r="H38" s="3">
+        <v>45901</v>
+      </c>
+      <c r="I38" s="2">
         <v>45929</v>
       </c>
       <c r="J38" s="9" t="s">
@@ -1967,32 +1968,32 @@
       <c r="A39" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B39" s="18" t="s">
+      <c r="B39" s="10" t="s">
         <v>32</v>
       </c>
       <c r="C39" s="9">
         <v>2025</v>
       </c>
-      <c r="D39" s="11">
-        <v>39</v>
-      </c>
-      <c r="E39" s="12">
-        <v>45929</v>
-      </c>
-      <c r="F39" s="10">
+      <c r="D39" s="1">
+        <v>39</v>
+      </c>
+      <c r="E39" s="2">
+        <v>45929</v>
+      </c>
+      <c r="F39" s="11">
         <v>45933</v>
       </c>
       <c r="G39" s="9">
         <v>1176</v>
       </c>
-      <c r="H39" s="13">
-        <v>45901</v>
-      </c>
-      <c r="I39" s="12">
+      <c r="H39" s="3">
+        <v>45901</v>
+      </c>
+      <c r="I39" s="2">
         <v>45929</v>
       </c>
       <c r="J39" s="9" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="K39" s="9" t="s">
         <v>11</v>
@@ -2002,28 +2003,28 @@
       <c r="A40" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B40" s="18" t="s">
+      <c r="B40" s="10" t="s">
         <v>32</v>
       </c>
       <c r="C40" s="9">
         <v>2025</v>
       </c>
-      <c r="D40" s="11">
-        <v>39</v>
-      </c>
-      <c r="E40" s="12">
-        <v>45929</v>
-      </c>
-      <c r="F40" s="10">
+      <c r="D40" s="1">
+        <v>39</v>
+      </c>
+      <c r="E40" s="2">
+        <v>45929</v>
+      </c>
+      <c r="F40" s="11">
         <v>45933</v>
       </c>
       <c r="G40" s="9">
         <v>907</v>
       </c>
-      <c r="H40" s="13">
-        <v>45901</v>
-      </c>
-      <c r="I40" s="12">
+      <c r="H40" s="3">
+        <v>45901</v>
+      </c>
+      <c r="I40" s="2">
         <v>45929</v>
       </c>
       <c r="J40" s="9" t="s">
@@ -2037,32 +2038,32 @@
       <c r="A41" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B41" s="18" t="s">
+      <c r="B41" s="10" t="s">
         <v>32</v>
       </c>
       <c r="C41" s="9">
         <v>2025</v>
       </c>
-      <c r="D41" s="11">
-        <v>39</v>
-      </c>
-      <c r="E41" s="12">
-        <v>45929</v>
-      </c>
-      <c r="F41" s="10">
+      <c r="D41" s="1">
+        <v>39</v>
+      </c>
+      <c r="E41" s="2">
+        <v>45929</v>
+      </c>
+      <c r="F41" s="11">
         <v>45933</v>
       </c>
       <c r="G41" s="9">
         <v>338</v>
       </c>
-      <c r="H41" s="13">
-        <v>45901</v>
-      </c>
-      <c r="I41" s="12">
+      <c r="H41" s="3">
+        <v>45901</v>
+      </c>
+      <c r="I41" s="2">
         <v>45929</v>
       </c>
       <c r="J41" s="9" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="K41" s="9" t="s">
         <v>11</v>
@@ -2072,28 +2073,28 @@
       <c r="A42" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B42" s="18" t="s">
+      <c r="B42" s="10" t="s">
         <v>32</v>
       </c>
       <c r="C42" s="9">
         <v>2025</v>
       </c>
-      <c r="D42" s="11">
-        <v>39</v>
-      </c>
-      <c r="E42" s="12">
-        <v>45929</v>
-      </c>
-      <c r="F42" s="10">
+      <c r="D42" s="1">
+        <v>39</v>
+      </c>
+      <c r="E42" s="2">
+        <v>45929</v>
+      </c>
+      <c r="F42" s="11">
         <v>45933</v>
       </c>
       <c r="G42" s="9">
         <v>339211</v>
       </c>
-      <c r="H42" s="13">
+      <c r="H42" s="3">
         <v>45870</v>
       </c>
-      <c r="I42" s="12">
+      <c r="I42" s="2">
         <v>45929</v>
       </c>
       <c r="J42" s="9" t="s">
@@ -2104,39 +2105,39 @@
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F43" s="3"/>
-      <c r="I43" s="3"/>
+      <c r="F43" s="15"/>
+      <c r="I43" s="15"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F44" s="3"/>
-      <c r="I44" s="3"/>
+      <c r="F44" s="15"/>
+      <c r="I44" s="15"/>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F45" s="3"/>
-      <c r="I45" s="3"/>
+      <c r="F45" s="15"/>
+      <c r="I45" s="15"/>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F46" s="3"/>
-      <c r="I46" s="3"/>
+      <c r="F46" s="15"/>
+      <c r="I46" s="15"/>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F47" s="3"/>
-      <c r="I47" s="3"/>
+      <c r="F47" s="15"/>
+      <c r="I47" s="15"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F48" s="3"/>
-      <c r="I48" s="3"/>
+      <c r="F48" s="15"/>
+      <c r="I48" s="15"/>
     </row>
     <row r="49" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F49" s="3"/>
-      <c r="I49" s="3"/>
+      <c r="F49" s="15"/>
+      <c r="I49" s="15"/>
     </row>
     <row r="50" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F50" s="3"/>
-      <c r="I50" s="3"/>
+      <c r="F50" s="15"/>
+      <c r="I50" s="15"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K32" xr:uid="{69362A46-9E44-40AB-81A2-018EE27C1DC6}">
+  <autoFilter ref="A1:K42" xr:uid="{69362A46-9E44-40AB-81A2-018EE27C1DC6}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K42">
       <sortCondition ref="B1:B32"/>
     </sortState>
@@ -2152,224 +2153,224 @@
   <dimension ref="A1:K22"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.7109375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.42578125" style="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="11" style="8"/>
+    <col min="1" max="1" width="7.7109375" style="16" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5703125" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" style="16" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.42578125" style="16" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.42578125" style="13" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14" style="16" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="11" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="17" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="11">
-        <v>2025</v>
-      </c>
-      <c r="D2" s="11">
-        <v>39</v>
-      </c>
-      <c r="E2" s="12">
-        <v>45929</v>
-      </c>
-      <c r="F2" s="10">
-        <v>45933</v>
-      </c>
-      <c r="G2" s="11">
+      <c r="C2" s="1">
+        <v>2025</v>
+      </c>
+      <c r="D2" s="1">
+        <v>39</v>
+      </c>
+      <c r="E2" s="2">
+        <v>45929</v>
+      </c>
+      <c r="F2" s="11">
+        <v>45933</v>
+      </c>
+      <c r="G2" s="1">
         <v>2857</v>
       </c>
-      <c r="H2" s="13">
-        <v>45901</v>
-      </c>
-      <c r="I2" s="12">
-        <v>45929</v>
-      </c>
-      <c r="J2" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="K2" s="11" t="s">
+      <c r="H2" s="3">
+        <v>45901</v>
+      </c>
+      <c r="I2" s="2">
+        <v>45929</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="11">
-        <v>2025</v>
-      </c>
-      <c r="D3" s="11">
-        <v>39</v>
-      </c>
-      <c r="E3" s="12">
-        <v>45929</v>
-      </c>
-      <c r="F3" s="10">
-        <v>45933</v>
-      </c>
-      <c r="G3" s="11">
+      <c r="C3" s="1">
+        <v>2025</v>
+      </c>
+      <c r="D3" s="1">
+        <v>39</v>
+      </c>
+      <c r="E3" s="2">
+        <v>45929</v>
+      </c>
+      <c r="F3" s="11">
+        <v>45933</v>
+      </c>
+      <c r="G3" s="1">
         <v>2771</v>
       </c>
-      <c r="H3" s="13">
-        <v>45901</v>
-      </c>
-      <c r="I3" s="12">
-        <v>45929</v>
-      </c>
-      <c r="J3" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="K3" s="11" t="s">
+      <c r="H3" s="3">
+        <v>45901</v>
+      </c>
+      <c r="I3" s="2">
+        <v>45929</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:11" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="11">
-        <v>2025</v>
-      </c>
-      <c r="D4" s="11">
-        <v>39</v>
-      </c>
-      <c r="E4" s="12">
-        <v>45929</v>
-      </c>
-      <c r="F4" s="10">
-        <v>45933</v>
-      </c>
-      <c r="G4" s="11">
+      <c r="C4" s="1">
+        <v>2025</v>
+      </c>
+      <c r="D4" s="1">
+        <v>39</v>
+      </c>
+      <c r="E4" s="2">
+        <v>45929</v>
+      </c>
+      <c r="F4" s="11">
+        <v>45933</v>
+      </c>
+      <c r="G4" s="1">
         <v>2273</v>
       </c>
-      <c r="H4" s="13">
-        <v>45901</v>
-      </c>
-      <c r="I4" s="12">
-        <v>45929</v>
-      </c>
-      <c r="J4" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="K4" s="11" t="s">
+      <c r="H4" s="3">
+        <v>45901</v>
+      </c>
+      <c r="I4" s="2">
+        <v>45929</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:11" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="11">
-        <v>2025</v>
-      </c>
-      <c r="D5" s="11">
-        <v>39</v>
-      </c>
-      <c r="E5" s="12">
-        <v>45929</v>
-      </c>
-      <c r="F5" s="10">
-        <v>45933</v>
-      </c>
-      <c r="G5" s="11">
+      <c r="C5" s="1">
+        <v>2025</v>
+      </c>
+      <c r="D5" s="1">
+        <v>39</v>
+      </c>
+      <c r="E5" s="2">
+        <v>45929</v>
+      </c>
+      <c r="F5" s="11">
+        <v>45933</v>
+      </c>
+      <c r="G5" s="1">
         <v>2051</v>
       </c>
-      <c r="H5" s="13">
-        <v>45901</v>
-      </c>
-      <c r="I5" s="12">
-        <v>45929</v>
-      </c>
-      <c r="J5" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="K5" s="11" t="s">
+      <c r="H5" s="3">
+        <v>45901</v>
+      </c>
+      <c r="I5" s="2">
+        <v>45929</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F6" s="3"/>
+      <c r="F6" s="15"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F7" s="3"/>
+      <c r="F7" s="15"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F8" s="3"/>
+      <c r="F8" s="15"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F9" s="3"/>
+      <c r="F9" s="15"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F10" s="3"/>
+      <c r="F10" s="15"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F11" s="3"/>
+      <c r="F11" s="15"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F12" s="3"/>
+      <c r="F12" s="15"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F13" s="3"/>
+      <c r="F13" s="15"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F14" s="3"/>
+      <c r="F14" s="15"/>
     </row>
     <row r="22" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F22" s="20"/>
+      <c r="F22" s="18"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Base/Backlog_39.xlsx
+++ b/Base/Backlog_39.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franciscoj\Python_Initial\Pyhton_Web\Base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58E55CD1-0406-4784-8F9C-9CE3A62DC907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09D3D05C-0C7F-41A9-83CD-5F0D95ACBAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="273" xr2:uid="{89A3EF9E-2AF9-420D-85DF-9BB5B68F651F}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="273" activeTab="1" xr2:uid="{89A3EF9E-2AF9-420D-85DF-9BB5B68F651F}"/>
   </bookViews>
   <sheets>
     <sheet name="ITI" sheetId="2" r:id="rId1"/>

--- a/Base/Backlog_39.xlsx
+++ b/Base/Backlog_39.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franciscoj\Python_Initial\Pyhton_Web\Base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09D3D05C-0C7F-41A9-83CD-5F0D95ACBAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37F8A32D-BEB4-4302-A9A8-E60C3ED4C50F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="273" activeTab="1" xr2:uid="{89A3EF9E-2AF9-420D-85DF-9BB5B68F651F}"/>
   </bookViews>
@@ -142,10 +142,10 @@
     <t>Sostenes Simões</t>
   </si>
   <si>
-    <t>Higor Jesus</t>
-  </si>
-  <si>
     <t>Resolvido</t>
+  </si>
+  <si>
+    <t>Higor Cruz</t>
   </si>
 </sst>
 </file>
@@ -1083,7 +1083,7 @@
         <v>45929</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K13" s="9" t="s">
         <v>11</v>
@@ -1118,7 +1118,7 @@
         <v>45929</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K14" s="9" t="s">
         <v>11</v>
@@ -1153,7 +1153,7 @@
         <v>45929</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K15" s="9" t="s">
         <v>11</v>
@@ -1188,7 +1188,7 @@
         <v>45929</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K16" s="9" t="s">
         <v>11</v>
@@ -1293,7 +1293,7 @@
         <v>45929</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K19" s="9" t="s">
         <v>11</v>
@@ -1328,7 +1328,7 @@
         <v>45929</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K20" s="9" t="s">
         <v>11</v>
@@ -1433,7 +1433,7 @@
         <v>45929</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K23" s="9" t="s">
         <v>11</v>
@@ -1503,7 +1503,7 @@
         <v>45929</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K25" s="9" t="s">
         <v>11</v>
@@ -1538,7 +1538,7 @@
         <v>45929</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K26" s="9" t="s">
         <v>11</v>
@@ -1713,7 +1713,7 @@
         <v>45929</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K31" s="9" t="s">
         <v>11</v>
@@ -1783,7 +1783,7 @@
         <v>45929</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K33" s="9" t="s">
         <v>11</v>
@@ -1993,7 +1993,7 @@
         <v>45929</v>
       </c>
       <c r="J39" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K39" s="9" t="s">
         <v>11</v>
@@ -2063,7 +2063,7 @@
         <v>45929</v>
       </c>
       <c r="J41" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K41" s="9" t="s">
         <v>11</v>
@@ -2266,7 +2266,7 @@
         <v>45929</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>15</v>
@@ -2277,7 +2277,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C4" s="1">
         <v>2025</v>
@@ -2301,7 +2301,7 @@
         <v>45929</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>15</v>
@@ -2336,7 +2336,7 @@
         <v>45929</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>15</v>

--- a/Base/Backlog_39.xlsx
+++ b/Base/Backlog_39.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franciscoj\Python_Initial\Pyhton_Web\Base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37F8A32D-BEB4-4302-A9A8-E60C3ED4C50F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5397A4B7-3D38-4C01-ABB9-351533F4F655}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="273" activeTab="1" xr2:uid="{89A3EF9E-2AF9-420D-85DF-9BB5B68F651F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="273" activeTab="1" xr2:uid="{89A3EF9E-2AF9-420D-85DF-9BB5B68F651F}"/>
   </bookViews>
   <sheets>
     <sheet name="ITI" sheetId="2" r:id="rId1"/>
@@ -94,9 +94,6 @@
     <t>Guilherme Worel</t>
   </si>
   <si>
-    <t>Denis Silva</t>
-  </si>
-  <si>
     <t>Mara Neves</t>
   </si>
   <si>
@@ -146,6 +143,9 @@
   </si>
   <si>
     <t>Higor Cruz</t>
+  </si>
+  <si>
+    <t>Denis da Silva</t>
   </si>
 </sst>
 </file>
@@ -674,7 +674,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C2" s="9">
         <v>2025</v>
@@ -709,7 +709,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C3" s="9">
         <v>2025</v>
@@ -744,7 +744,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C4" s="9">
         <v>2025</v>
@@ -779,7 +779,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C5" s="9">
         <v>2025</v>
@@ -814,7 +814,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C6" s="9">
         <v>2025</v>
@@ -849,7 +849,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C7" s="9">
         <v>2025</v>
@@ -884,7 +884,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C8" s="9">
         <v>2025</v>
@@ -919,7 +919,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C9" s="9">
         <v>2025</v>
@@ -954,7 +954,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C10" s="9">
         <v>2025</v>
@@ -989,7 +989,7 @@
         <v>4</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" s="9">
         <v>2025</v>
@@ -1024,7 +1024,7 @@
         <v>4</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C12" s="9">
         <v>2025</v>
@@ -1059,7 +1059,7 @@
         <v>4</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C13" s="9">
         <v>2025</v>
@@ -1083,7 +1083,7 @@
         <v>45929</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K13" s="9" t="s">
         <v>11</v>
@@ -1094,7 +1094,7 @@
         <v>4</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C14" s="9">
         <v>2025</v>
@@ -1118,7 +1118,7 @@
         <v>45929</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K14" s="9" t="s">
         <v>11</v>
@@ -1129,7 +1129,7 @@
         <v>4</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C15" s="9">
         <v>2025</v>
@@ -1153,7 +1153,7 @@
         <v>45929</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K15" s="9" t="s">
         <v>11</v>
@@ -1164,7 +1164,7 @@
         <v>4</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C16" s="9">
         <v>2025</v>
@@ -1188,7 +1188,7 @@
         <v>45929</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K16" s="9" t="s">
         <v>11</v>
@@ -1199,7 +1199,7 @@
         <v>4</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C17" s="9">
         <v>2025</v>
@@ -1234,7 +1234,7 @@
         <v>4</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C18" s="9">
         <v>2025</v>
@@ -1269,7 +1269,7 @@
         <v>4</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C19" s="9">
         <v>2025</v>
@@ -1293,7 +1293,7 @@
         <v>45929</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K19" s="9" t="s">
         <v>11</v>
@@ -1328,7 +1328,7 @@
         <v>45929</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K20" s="9" t="s">
         <v>11</v>
@@ -1433,7 +1433,7 @@
         <v>45929</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K23" s="9" t="s">
         <v>11</v>
@@ -1479,7 +1479,7 @@
         <v>4</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C25" s="9">
         <v>2025</v>
@@ -1503,7 +1503,7 @@
         <v>45929</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K25" s="9" t="s">
         <v>11</v>
@@ -1514,7 +1514,7 @@
         <v>4</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C26" s="9">
         <v>2025</v>
@@ -1538,7 +1538,7 @@
         <v>45929</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K26" s="9" t="s">
         <v>11</v>
@@ -1549,7 +1549,7 @@
         <v>4</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C27" s="9">
         <v>2025</v>
@@ -1584,7 +1584,7 @@
         <v>4</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C28" s="9">
         <v>2025</v>
@@ -1619,7 +1619,7 @@
         <v>4</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C29" s="9">
         <v>2025</v>
@@ -1654,7 +1654,7 @@
         <v>4</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C30" s="9">
         <v>2025</v>
@@ -1689,7 +1689,7 @@
         <v>4</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C31" s="9">
         <v>2025</v>
@@ -1713,7 +1713,7 @@
         <v>45929</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K31" s="9" t="s">
         <v>11</v>
@@ -1724,7 +1724,7 @@
         <v>4</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C32" s="9">
         <v>2025</v>
@@ -1759,7 +1759,7 @@
         <v>4</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C33" s="9">
         <v>2025</v>
@@ -1783,7 +1783,7 @@
         <v>45929</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K33" s="9" t="s">
         <v>11</v>
@@ -1794,7 +1794,7 @@
         <v>4</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C34" s="9">
         <v>2025</v>
@@ -1829,7 +1829,7 @@
         <v>4</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C35" s="9">
         <v>2025</v>
@@ -1864,7 +1864,7 @@
         <v>4</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C36" s="9">
         <v>2025</v>
@@ -1899,7 +1899,7 @@
         <v>4</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C37" s="9">
         <v>2025</v>
@@ -1934,7 +1934,7 @@
         <v>4</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C38" s="9">
         <v>2025</v>
@@ -1969,7 +1969,7 @@
         <v>4</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C39" s="9">
         <v>2025</v>
@@ -1993,7 +1993,7 @@
         <v>45929</v>
       </c>
       <c r="J39" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K39" s="9" t="s">
         <v>11</v>
@@ -2004,7 +2004,7 @@
         <v>4</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C40" s="9">
         <v>2025</v>
@@ -2039,7 +2039,7 @@
         <v>4</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C41" s="9">
         <v>2025</v>
@@ -2063,7 +2063,7 @@
         <v>45929</v>
       </c>
       <c r="J41" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K41" s="9" t="s">
         <v>11</v>
@@ -2074,7 +2074,7 @@
         <v>4</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C42" s="9">
         <v>2025</v>
@@ -2207,7 +2207,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C2" s="1">
         <v>2025</v>
@@ -2242,7 +2242,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C3" s="1">
         <v>2025</v>
@@ -2266,7 +2266,7 @@
         <v>45929</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>15</v>
@@ -2277,7 +2277,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C4" s="1">
         <v>2025</v>
@@ -2301,7 +2301,7 @@
         <v>45929</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>15</v>
@@ -2312,7 +2312,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C5" s="1">
         <v>2025</v>
@@ -2336,7 +2336,7 @@
         <v>45929</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>15</v>
